--- a/tests/fixtures/out/export_engine_merge.xlsx
+++ b/tests/fixtures/out/export_engine_merge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>region</t>
   </si>
@@ -406,11 +406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="5" spans="1:4"/>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>6</v>
@@ -422,21 +418,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="7" spans="1:4"/>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:D2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
